--- a/data/daily/2026-09/2026-09-17.xlsx
+++ b/data/daily/2026-09/2026-09-17.xlsx
@@ -1245,14 +1245,89 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="323850" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1267,17 +1342,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="361950" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1292,110 +1367,35 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1500,157 +1500,157 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="866775" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="990600" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -2600,24 +2600,20 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>편리한 개별 포장 및 섭취법 — 액상과 정제가 함께 들어있는 개별 포장 형태로 외출이나 여행 시 간편하게 섭취 가능함</t>
+          <t>편리한 휴대성과 섭취 — 액상과 정제 일체형 및 개별 개별 소분 포장으로 휴대와 매일 섭취가 간편함</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>부담 없는 새콤달콤한 맛 — 상큼하고 새콤달콤한 액상 맛으로 공복에 먹어도 거부감이 없음</t>
+          <t>뛰어난 피로회복 효과 — 복용 후 컨디션이 덜 처지고 활력이 충전되는 느낌을 체감함</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>선물용으로 높은 만족도 — 응원 메시지와 함께 주고받기 좋아 생일이나 일상 선물용으로 적합함</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>즉각적인 체감 효과 미비 — 섭취 후 드라마틱한 신체 변화를 바로 느끼기에는 어려움이 있음</t>
-        </is>
-      </c>
+          <t>부담 없는 새콤한 맛 — 맛이 새콤달콤하고 상큼하여 아침 공복에 마시기에도 부담이 없음</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
@@ -2663,17 +2659,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>물 없이 간편한 오렌지맛 섭취 — 오렌지 맛 액상 형태로 물 없이 어디서나 휴대하며 즉시 먹기 편함</t>
+          <t>우수한 피로 회복 — 복용 후 활력이 생기고 피로감이 확실히 덜한 느낌을 받음</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>고급스러운 포장과 카 구성 — 선물 패키지가 고급스럽고 메시지 카드가 동봉되어 선물용으로 훌륭함</t>
+          <t>고급스러운 선물 포장 — 선물 포장이 매우 깔끔하며 메시지 카드까지 동봉되어 선물용으로 매우 유용함</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>피로 회복 및 활력 충전 — 고함량 비타민과 필수 미네랄 구성으로 피로를 줄이고 활력을 높이는 데 도움 됨</t>
+          <t>간편한 복용 방법 — 물 없이 어디서나 편하게 섭취할 수 있고 병 타입이라 휴대하기 편함</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -2722,18 +2718,18 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>피로 회복 및 컨디션 개선 — 꾸준히 먹으면 피로감이 줄어들고 몸에 힘이 나는 느낌을 받음</t>
+          <t>확실한 피로 개선 — 섭취한 뒤 피로가 풀리고 덜 피곤하며 힘이 나는 효과를 체감함</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>고급스러운 기프트 포장 — 포장이 고급스럽게 잘 되어 있어 추석 등 명절 선물용으로 주고받기 좋음</t>
+          <t>고급스러운 포장 — 포장 상태가 우수하고 고급스러워 선물용이나 자가 건강 관리용으로 만족스러움</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>구매 직후 가격 인하 — 제품 수령 직후 판매 가격이 내려가 가격 차이에 대한 아쉬움이 남음</t>
+          <t>아쉬운 가격 변동 — 구매 직후 제품 가격이 만 원 이상 추가 인하되어 아쉬움이 남음</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -2781,22 +2777,22 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>피로감 완화 및 생기 회복 — 섭취 후 피로감이 줄어들고 몸의 생기를 되찾는 데 효과적임</t>
+          <t>피로 및 생기 회복 — 꾸준히 복용한 후 피로감이 줄어들고 몸의 상태가 호전됨을 느낌</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>알찬 추가 증정 구성 — 단독 에디션으로 본품 외에 추가 증정량이 들어있어 풍성하고 만족스러움</t>
+          <t>알찬 추가 증정 구성 — 카카오 선물하기 전 전용 단독 에디션으로 증정 혜택이 있어 구성이 풍성함</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>한 번에 챙기는 올인원 방식 — 여러 영양제를 따로 먹지 않고 한 번에 간편히 챙길 수 있음</t>
+          <t>간편한 섭취 방식 — 여러 영양제를 따로 챙길 필요 없이 한 번에 간편하게 복용 가능함</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>섭취 후 소변 색 변화 — 비타민 성분으로 인해 섭취 후 하루 종일 소변 색이 진한 노란색으로 변함</t>
+          <t>소변 색상 변화 — 복용 후 소변 색이 진한 노란색으로 변하여 일시적으로 놀라거나 의구심이 생길 수 있음</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
@@ -2844,24 +2840,20 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>목넘김이 쉬운 알약 크기 — 정제 크기가 크지 않아 알약을 잘 삼키지 못하는 사람도 쉽게 복용 가능함</t>
+          <t>신속한 피로 회복 — 체력이 떨어졌거나 피곤할 때 복용하면 빠르게 컨디션이 회복됨</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>빠른 컨디션 회복 체감 — 피로가 쌓였을 때 하나씩 먹으면 컨디션이 회복되고 힘이 나는 느낌을 줌</t>
+          <t>작고 편안한 알약 크기 — 동봉된 알약의 크기가 크지 않아 목넘김 시 어려움 없이 삼키기 편함</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>정성스러운 선물용 패키지 — 선물 포장이 이쁘고 고급스러워 받는 사람의 만족도가 높음</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>진해서 용기에 남는 액상 제형 — 액상이 매우 진하여 남기지 않으려면 물로 헹궈 마셔야 하는 불편함이 있음</t>
-        </is>
-      </c>
+          <t>편리한 올인원 섭취 — 귀찮은 영양제 복용 과정을 생략하고 멀티비타민 한 병으로 해결할 수 있어 만족함</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
@@ -2903,22 +2895,22 @@
         <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>6466</v>
+        <v>6467</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>맛있는 젤리 형태의 섭취 — 알약에 거부감이 있는 사람도 부담 없이 맛있게 먹을 수 있는 구미 제형임</t>
+          <t>맛있는 젤리 제형 — 알약 거부감이 있는 사람도 간식이나 젤리를 먹는 것처럼 맛있게 먹을 수 있음</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>꾸준한 복용 용이성 — 간식처럼 챙겨 먹기 편해 잊지 않고 매일 꼬박꼬박 챙겨 먹기 좋음</t>
+          <t>꾸준한 섭취 습관 형성 — 복용이 즐거워 귀찮아하지 않고 매일 잊지 않고 챙겨 먹게 됨</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>효능 체감의 불확실성 — 맛은 좋으나 영양제로서의 직접적인 효과는 바로 체감하기 어려움</t>
+          <t>미미한 효과 체감 — 맛과 복용 편의성은 좋으나 실제 몸이 나아지는 등의 뚜렷한 효과를 인지하기 어려움</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
@@ -2966,18 +2958,18 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>피로 회복 및 활력 보충 — 컨디션이 안 좋거나 피로할 때 빠른 회복과 에너지를 제공함</t>
+          <t>탁월한 컨디션 회복 — 몸의 상태가 안 좋거나 많이 피곤할 때 섭취 후 피로 회복 및 생기 충전에 큰 도움을 받음</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>간편한 휴대성과 맛 — 맛이 좋고 휴대 및 마시기가 편하여 지인 선물용으로 인기가 높음</t>
+          <t>우수한 편의성 — 맛이 좋고 개별 병 타입으로 포장되어 가지고 다니며 먹기에 용이함</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>다소 높은 가격대 — 제품의 가격대가 다소 비싸게 형성되어 있음</t>
+          <t>높은 가격대 — 인기 있고 신뢰할 수 있는 제품이나 상시 복용하기에는 다소 비싼 편임</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -3025,24 +3017,20 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>고급스러운 포장 디자인 — 빈 병도 버리기 아까울 정도로 포장이 매우 고급스러워 선물용으로 훌륭함</t>
+          <t>높은 브랜드 신뢰도 — 신뢰성 높은 정관장 브랜드 제품으로 받는 사람에게 믿음을 주는 기분 좋은 선물임</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>부담 없는 새콤달콤한 맛 — 맛이 달콤하고 새콤하여 부담 없이 편하게 복용 가능함</t>
+          <t>독특하고 간편한 제형 — 액상과 분말을 함께 섞어 먹는 독특한 복용 방식이며 맛이 달콤새콤하여 목넘김이 편함</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>높은 브랜드 신뢰도 — 정관장 브랜드 제품이라 선물받았을 때 신뢰감이 높음</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>초반의 생소한 복용 방식 — 액상과 분말을 섞어 먹는 특이한 용기 방식이 처음에는 낯설 수 있음</t>
-        </is>
-      </c>
+          <t>고급스러운 포장 디자인 — 패키지 포장이 견고하고 매우 고급스러워 선물용 및 병 수집용으로 훌륭함</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
@@ -3088,15 +3076,19 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>작은 용기 속 뛰어난 효능 — 작은 병 하나에 음료와 정제가 함께 들어있어 피로 회복에 탁월함</t>
+          <t>강력한 피로 회복 — 피곤하고 지칠 때 하나씩 마셔주면 개운해지고 피로가 해소되는 효과를 얻음</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>고급스러운 패키지 구성 — 패키지가 귀엽고 고급스러우며 젤리 증정 등이 포함되어 선물용으로 매우 좋음</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>영양 가득한 소형 패키지 — 작은 병 하나에 뛰어난 영양 성분의 액상과 알약이 모두 들어있어 매우 알참</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>훌륭한 맛과 패키지 — 맛이 좋으며 추석 등 시즌 패키지가 매우 화려하고 고급스러워 소장 가치가 높음</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
@@ -3143,18 +3135,18 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>오래 지속되는 활력 효과 — 꾸준히 복용 시 피로감이 줄어들고 몸의 활력이 오래 유지됨</t>
+          <t>뛰어난 피로 개선 지속력 — 피로 회복 효과의 지속력이 길고 반짝이는 듯한 개운한 컨디션이 오래 유지됨</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>정성스러운 포장 품질 — 디자인과 포장이 매우 고급스러워 선물받았을 때 기분이 좋음</t>
+          <t>성별 맞춤형 설계 — 남성용(m)과 여성용(f)을 선택하여 복용할 수 있어 성향 및 필요 영양소 배합에 알맞음</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>삼키기 부담스러운 알약 크기 — 기존 제품 대비 정제 크기가 커서 삼킬 때 다소 걸리는 느낌이 있음</t>
+          <t>부담스러운 알약 크기 — 기존 제품들에 비해 알약의 크기가 다소 커서 삼키기 어려울 수 있음</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -3202,18 +3194,22 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>편안한 소화 및 배변 도움 — 식사 후 더부룩함을 줄여 소화를 돕고 배변 활동을 원활하게 만듦</t>
+          <t>소화 및 배변 개선 — 식사 후 복용 시 소화가 편안하게 잘되고 배변 활동을 활발하게 해 줌</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>고소한 군고구마 맛 — 군고구마 맛이 나 거부감 없이 고소하고 맛있게 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>고소하고 부담 없는 맛 — 군고구마 맛이 연상되는 고소한 맛으로 비리거나 부담스럽지 않게 섭취 가능함</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>풍성한 사은품과 특가 — 할인 가격 혜택이 우수하며 사은품이나 한정 혜택 구성이 다채로움</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>구매 수량 제한의 불편함 — 선물용으로 대량 구매를 원해도 2개로 구매 수량이 제한되어 있음</t>
+          <t>제한적인 구매 수량 — 구매 가능한 수량 제한이 적용되어 여러 명에게 한 번에 대량으로 선물하기가 어려움</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -3261,18 +3257,18 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>말차와 딸기의 맛있는 조합 — 말차향과 딸기맛이 잘 어우러져 거부감 없이 맛있게 섭취 가능함</t>
+          <t>훌륭한 맛의 조화 — 말차와 딸기의 맛이 적절하게 조합되어 특유의 텁텁함 없이 매우 맛있게 섭취 가능함</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>아이돌 포토카드 혜택 — 콜라보 제품으로 포토카드와 엽서가 함께 제공되어 팬들의 만족도가 높음</t>
+          <t>알찬 콜라보 굿즈 제공 — 리센느 멤버의 포토카드와 엽서가 기본 포함되어 소장 욕구를 지닌 팬들에게 인기가 많음</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>기존 효소 대비 적은 용량 — 기존에 판매하던 효소 제품에 비해 1포당 용량이 절반 정도로 적음</t>
+          <t>상대적으로 적은 용량 — 브랜드의 기존 다른 일반 카무트 효소 제품들과 비교 시 용량이 거의 반 정도에 그침</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -3320,12 +3316,12 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>정성스럽고 화려한 선물 포장 — 은은한 핑크 색상과 고급스러운 오간자 포장으로 선물 가치가 높음</t>
+          <t>매우 아름다운 선물 포장 — 은은한 핑크 오간자 리본 포장 등으로 정성과 고급스러움을 극대화하여 선물 가치를 높임</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>맑고 탱탱해지는 피부 체감 — 꾸준히 먹으면 피부가 탱탱해지고 맑아지는 느낌을 받음</t>
+          <t>피부 개선 및 편한 복용 — 액상 앰플 형태라 편하게 복용할 수 있으며 피부가 한결 맑아지고 탄력 있어지는 느낌을 줌</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -3375,23 +3371,23 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>알찬 증정품과 가성비 — 저렴한 가격에 추가 증정 포와 과자까지 사은품으로 제공되어 혜택이 좋음</t>
+          <t>탁월한 소화 개선 효과 — 속이 더부룩하거나 소화가 잘 안 될 때 복용하면 뱃속이 한결 편안해짐</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>맛있고 속 편한 소화 서포트 — 맛이 좋아 부담이 없으며 식사 후 소화에 도움을 줌</t>
+          <t>가성비와 풍성한 증정 — 비교적 가격이 저렴하고 추가 증정 10포와 파로저당씬칩 과자 사은품까지 주어 만족스러움</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>섭취 초반의 장 반응 — 복용 후 뱃속이 꾸르륵거리거나 방귀가 자주 나오는 현상이 있음</t>
+          <t>구매 수량 제한의 불편 — 우수한 제품임에도 최대 2개 이상 구매하지 못하도록 수량이 한정되어 다량 구매가 불가능함</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>최대 구매 수량 제한 — 1인당 최대 2개까지만 구매 가능하도록 수량이 제한되어 있음</t>
+          <t>초기 복부 팽만 및 가스 — 섭취 후 뱃속이 가스가 차서 꾸르륵거리거나 방귀가 자주 배출되는 반응이 일시적으로 나타남</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -3438,23 +3434,27 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>골라 먹는 다양한 맛 구성 — 다양한 종류의 닭가슴살이 들어있어 질리지 않고 매일 골라 먹기 좋음</t>
+          <t>질리지 않는 다양한 맛 — 종류가 다채롭게 구성되어 한 달간 지루하지 않게 골라 먹기 좋고 전반적으로 맛이 훌륭함</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>실용적인 보냉백 증정 — 가격 대비 양이 푸짐하며 도시락용 보냉백까지 증정되어 활용도가 높음</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
+          <t>실용적인 보냉백 증정 — 증정되는 보냉파우치의 크기가 넉넉하고 실용적이어서 평소 도시락을 싸 다닐 때 편리함</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>합리적인 세트 가격 — 식단 관리를 위한 대용량 팩을 매우 경제적인 가격대에 풍성하게 구매할 수 있음</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>배송 중 포장 터짐 현상 — 비닐 진공 포장이 헐렁하여 일부 제품이 터지고 소스가 새어 나오는 경우가 있음</t>
+          <t>일부 팩의 포장 불량 — 진공포장이 불량하여 헐렁거리거나 배송 중에 터져 내용물 및 소스가 새어 나옴</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>배송 시 제품 해동 — 배송 과정에서 제품이 많이 녹은 상태로 수령되는 사례가 있음</t>
+          <t>배송 중 해동 발생 — 냉동 상태로 신속히 도달하지 못해 수령 시점에 이미 해동이 꽤 진행되어 있음</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -3501,18 +3501,22 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>부드럽고 촉촉한 식감 — 닭가슴살 특유의 퍽퍽함이 전혀 없고 매우 부드러움</t>
+          <t>부드럽고 훌륭한 식감 — 닭가슴살 특유의 뻑뻑함이 느껴지지 않을 정도로 부드러우며 자극적이지 않고 담백함</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>가성비 좋은 패키지 구성 — 저렴한 가격대에 다양한 메뉴가 구성되어 다이어트 식단으로 적합함</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
+          <t>가성비 넘치는 패키지 — 대량의 닭가슴살 팩을 3만 원 이하의 저렴하고 합리적인 비용에 구매할 수 있음</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>간편하고 다양한 메뉴 — 메뉴가 획일적이지 않아 질리지 않고 물리지 않으며 전자레인지 간편 조리가 편리함</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>배송 중 제품 해동 — 냉동 상태로 와야 할 제품이 배송 중 녹아서 도착하는 문제가 있음</t>
+          <t>배송 중 해동 현상 — 배송 도중 아이스팩 기능 저하 등의 문제로 수령 시 전제품이 해동되어 배송됨</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
@@ -3560,17 +3564,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>단백질 특유의 비린 맛 없음 — 텁텁함이나 비린 맛이 없고 일반 우유나 음료처럼 달콤하고 깔끔함</t>
+          <t>깔끔하고 비리지 않은 맛 — 단백질 특유의 텁텁함과 비린 느낌이 없고 편의점 초코우유나 커피라떼처럼 맛있고 말끔함</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>속 편한 분리유청단백질 — 소화가 편한 성분으로 마신 후에도 속이 더부룩하지 않고 편안함</t>
+          <t>이상적인 영양 구성 — 단백질 20g을 포함한 풍부한 함량 대비 칼로리와 당이 낮아 부담 없이 다이어트에 활용함</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>휴대하기 편한 패키지 — 슬림한 용기로 가방에 넣고 다니며 운동 전후나 간식으로 마시기 용이함</t>
+          <t>편안한 소화감 — 분리유청단백질이라서 마신 뒤에도 배앓이나 속 더부룩함이 유발되지 않고 속이 아주 편안함</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -3619,17 +3623,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>신뢰할 수 있는 모델 추천 세트 — 김종국 추천 조합으로 아르기닌과 밀크씨슬을 함께 챙길 수 있어 알참</t>
+          <t>체감되는 피로 회복 — 아침에 일어날 때 몸이 가볍고 야근이나 운동 전후 활력과 지속력 보완에 효능이 뛰어남</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>확연한 피로 회복 및 활력 증진 — 아침에 일어날 때 몸이 가볍고 운동 시 지치지 않는 컨디션 유지에 도움 됨</t>
+          <t>알차고 유용한 조합 — 피로 복구를 돕는 아르기닌 마카와 간 개선용 밀크씨슬을 합쳐 종합적 관리가 쉬움</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>쇼핑백 증정으로 선물에 적합 — 고급스러운 쇼핑백이 함께 포함되어 지인이나 직장 동료 선물용으로 좋음</t>
+          <t>선물하기 좋은 고급 구성 — 쇼핑백이 기본 동봉되어 직장동료나 지인들의 축하 선물 및 건강 응원용으로 어울림</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -3639,7 +3643,7 @@
     <row r="20" ht="38" customHeight="1">
       <c r="B20" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -3647,51 +3651,51 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
+          <t>'1입 증정' 아일로 타입1 콜라겐 비오틴 앰플 14일분 오간자 에디션 + 앰플 1입 추가 증정</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>아일로</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>43,900원</t>
+          <t>34,900원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7417420</t>
+          <t>https://gift.kakao.com/product/4965673</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260706153340_3e124da6e254462d9a7efad2521e3b9e.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260907090314_deefdfac70e6456194d7f4950eb47fcb.jpg</t>
         </is>
       </c>
       <c r="I20" t="n">
         <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>248</v>
+        <v>757</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>6200mg 초고함량 활력 충전 — 높은 아르기닌 함량으로 운동 퍼포먼스 향상과 피로 회복에 탁월함</t>
+          <t>상큼하고 비리지 않은 맛 — 가루형 특유의 냄새를 없애고 과일 맛의 상큼한 액상을 사용해 삼키기 좋고 비리지 않음</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>고급스러운 선물용 구성 — 패키지가 고급스럽고 추가 포와 전용 쇼핑백이 증정되어 선물용으로 뛰어남</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>간편한 1포 섭취 및 휴대성 — 개별 포장되어 외출이나 운동 전 간편하게 1포씩 챙겨 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>공주풍의 예쁜 패키지 — 케이스와 병 외관 디자인이 무척 사랑스럽고 화려하여 시각적 만족감이 높음</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>다소 진한 액상 제형 — 액상이 고농축되어 맛이 다소 진하거나 강해 섭취 후 물을 한 잔 마셔야 할 수 있음</t>
+        </is>
+      </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
     </row>
@@ -3737,15 +3741,19 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>상큼한 레몬 맛의 액상 제형 — 액상 스틱 형태로 물에 타서 부담 없이 맛있게 마실 수 있음</t>
+          <t>에너지 충전 및 활력 — 웨이트 트레이닝 전후 피로 개선과 활력 보완 및 근육 회복 보조에 도움을 줌</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>운동 및 일상 활력 증진 — 복용 시 하루 시작이 가벼워지고 운동할 때 피로 회복과 기력 보충에 도움 됨</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
+          <t>편리한 액상과 좋은 맛 — 상큼한 레몬 맛의 액상 제형으로 물에 간편하게 희석해 먹기에 거부감이 없음</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>뛰어난 휴대성 — 개별 슬림한 액상 스틱 형태로 제작되어 외출 시나 주머니에 간편히 챙기기 용이함</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
@@ -4083,7 +4091,7 @@
         <v>783</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>6466</v>
+        <v>6467</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>734</v>
@@ -4106,67 +4114,68 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>편리한 개별 포장 및 섭취법 — 액상과 정제가 함께 들어있는 개별 포장 형태로 외출이나 여행 시 간편하게 섭취 가능함
-부담 없는 새콤달콤한 맛 — 상큼하고 새콤달콤한 액상 맛으로 공복에 먹어도 거부감이 없음
-선물용으로 높은 만족도 — 응원 메시지와 함께 주고받기 좋아 생일이나 일상 선물용으로 적합함</t>
+          <t>편리한 휴대성과 섭취 — 액상과 정제 일체형 및 개별 개별 소분 포장으로 휴대와 매일 섭취가 간편함
+뛰어난 피로회복 효과 — 복용 후 컨디션이 덜 처지고 활력이 충전되는 느낌을 체감함
+부담 없는 새콤한 맛 — 맛이 새콤달콤하고 상큼하여 아침 공복에 마시기에도 부담이 없음</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>물 없이 간편한 오렌지맛 섭취 — 오렌지 맛 액상 형태로 물 없이 어디서나 휴대하며 즉시 먹기 편함
-고급스러운 포장과 카 구성 — 선물 패키지가 고급스럽고 메시지 카드가 동봉되어 선물용으로 훌륭함
-피로 회복 및 활력 충전 — 고함량 비타민과 필수 미네랄 구성으로 피로를 줄이고 활력을 높이는 데 도움 됨</t>
+          <t>우수한 피로 회복 — 복용 후 활력이 생기고 피로감이 확실히 덜한 느낌을 받음
+고급스러운 선물 포장 — 선물 포장이 매우 깔끔하며 메시지 카드까지 동봉되어 선물용으로 매우 유용함
+간편한 복용 방법 — 물 없이 어디서나 편하게 섭취할 수 있고 병 타입이라 휴대하기 편함</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>피로 회복 및 컨디션 개선 — 꾸준히 먹으면 피로감이 줄어들고 몸에 힘이 나는 느낌을 받음
-고급스러운 기프트 포장 — 포장이 고급스럽게 잘 되어 있어 추석 등 명절 선물용으로 주고받기 좋음</t>
+          <t>확실한 피로 개선 — 섭취한 뒤 피로가 풀리고 덜 피곤하며 힘이 나는 효과를 체감함
+고급스러운 포장 — 포장 상태가 우수하고 고급스러워 선물용이나 자가 건강 관리용으로 만족스러움</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>피로감 완화 및 생기 회복 — 섭취 후 피로감이 줄어들고 몸의 생기를 되찾는 데 효과적임
-알찬 추가 증정 구성 — 단독 에디션으로 본품 외에 추가 증정량이 들어있어 풍성하고 만족스러움
-한 번에 챙기는 올인원 방식 — 여러 영양제를 따로 먹지 않고 한 번에 간편히 챙길 수 있음</t>
+          <t>피로 및 생기 회복 — 꾸준히 복용한 후 피로감이 줄어들고 몸의 상태가 호전됨을 느낌
+알찬 추가 증정 구성 — 카카오 선물하기 전 전용 단독 에디션으로 증정 혜택이 있어 구성이 풍성함
+간편한 섭취 방식 — 여러 영양제를 따로 챙길 필요 없이 한 번에 간편하게 복용 가능함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>목넘김이 쉬운 알약 크기 — 정제 크기가 크지 않아 알약을 잘 삼키지 못하는 사람도 쉽게 복용 가능함
-빠른 컨디션 회복 체감 — 피로가 쌓였을 때 하나씩 먹으면 컨디션이 회복되고 힘이 나는 느낌을 줌
-정성스러운 선물용 패키지 — 선물 포장이 이쁘고 고급스러워 받는 사람의 만족도가 높음</t>
+          <t>신속한 피로 회복 — 체력이 떨어졌거나 피곤할 때 복용하면 빠르게 컨디션이 회복됨
+작고 편안한 알약 크기 — 동봉된 알약의 크기가 크지 않아 목넘김 시 어려움 없이 삼키기 편함
+편리한 올인원 섭취 — 귀찮은 영양제 복용 과정을 생략하고 멀티비타민 한 병으로 해결할 수 있어 만족함</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 젤리 형태의 섭취 — 알약에 거부감이 있는 사람도 부담 없이 맛있게 먹을 수 있는 구미 제형임
-꾸준한 복용 용이성 — 간식처럼 챙겨 먹기 편해 잊지 않고 매일 꼬박꼬박 챙겨 먹기 좋음</t>
+          <t>맛있는 젤리 제형 — 알약 거부감이 있는 사람도 간식이나 젤리를 먹는 것처럼 맛있게 먹을 수 있음
+꾸준한 섭취 습관 형성 — 복용이 즐거워 귀찮아하지 않고 매일 잊지 않고 챙겨 먹게 됨</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>피로 회복 및 활력 보충 — 컨디션이 안 좋거나 피로할 때 빠른 회복과 에너지를 제공함
-간편한 휴대성과 맛 — 맛이 좋고 휴대 및 마시기가 편하여 지인 선물용으로 인기가 높음</t>
+          <t>탁월한 컨디션 회복 — 몸의 상태가 안 좋거나 많이 피곤할 때 섭취 후 피로 회복 및 생기 충전에 큰 도움을 받음
+우수한 편의성 — 맛이 좋고 개별 병 타입으로 포장되어 가지고 다니며 먹기에 용이함</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 포장 디자인 — 빈 병도 버리기 아까울 정도로 포장이 매우 고급스러워 선물용으로 훌륭함
-부담 없는 새콤달콤한 맛 — 맛이 달콤하고 새콤하여 부담 없이 편하게 복용 가능함
-높은 브랜드 신뢰도 — 정관장 브랜드 제품이라 선물받았을 때 신뢰감이 높음</t>
+          <t>높은 브랜드 신뢰도 — 신뢰성 높은 정관장 브랜드 제품으로 받는 사람에게 믿음을 주는 기분 좋은 선물임
+독특하고 간편한 제형 — 액상과 분말을 함께 섞어 먹는 독특한 복용 방식이며 맛이 달콤새콤하여 목넘김이 편함
+고급스러운 포장 디자인 — 패키지 포장이 견고하고 매우 고급스러워 선물용 및 병 수집용으로 훌륭함</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>작은 용기 속 뛰어난 효능 — 작은 병 하나에 음료와 정제가 함께 들어있어 피로 회복에 탁월함
-고급스러운 패키지 구성 — 패키지가 귀엽고 고급스러우며 젤리 증정 등이 포함되어 선물용으로 매우 좋음</t>
+          <t>강력한 피로 회복 — 피곤하고 지칠 때 하나씩 마셔주면 개운해지고 피로가 해소되는 효과를 얻음
+영양 가득한 소형 패키지 — 작은 병 하나에 뛰어난 영양 성분의 액상과 알약이 모두 들어있어 매우 알참
+훌륭한 맛과 패키지 — 맛이 좋으며 추석 등 시즌 패키지가 매우 화려하고 고급스러워 소장 가치가 높음</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>오래 지속되는 활력 효과 — 꾸준히 복용 시 피로감이 줄어들고 몸의 활력이 오래 유지됨
-정성스러운 포장 품질 — 디자인과 포장이 매우 고급스러워 선물받았을 때 기분이 좋음</t>
+          <t>뛰어난 피로 개선 지속력 — 피로 회복 효과의 지속력이 길고 반짝이는 듯한 개운한 컨디션이 오래 유지됨
+성별 맞춤형 설계 — 남성용(m)과 여성용(f)을 선택하여 복용할 수 있어 성향 및 필요 영양소 배합에 알맞음</t>
         </is>
       </c>
     </row>
@@ -4176,46 +4185,34 @@
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>즉각적인 체감 효과 미비 — 섭취 후 드라마틱한 신체 변화를 바로 느끼기에는 어려움이 있음</t>
-        </is>
-      </c>
+      <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>구매 직후 가격 인하 — 제품 수령 직후 판매 가격이 내려가 가격 차이에 대한 아쉬움이 남음</t>
+          <t>아쉬운 가격 변동 — 구매 직후 제품 가격이 만 원 이상 추가 인하되어 아쉬움이 남음</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>섭취 후 소변 색 변화 — 비타민 성분으로 인해 섭취 후 하루 종일 소변 색이 진한 노란색으로 변함</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>진해서 용기에 남는 액상 제형 — 액상이 매우 진하여 남기지 않으려면 물로 헹궈 마셔야 하는 불편함이 있음</t>
-        </is>
-      </c>
+          <t>소변 색상 변화 — 복용 후 소변 색이 진한 노란색으로 변하여 일시적으로 놀라거나 의구심이 생길 수 있음</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>효능 체감의 불확실성 — 맛은 좋으나 영양제로서의 직접적인 효과는 바로 체감하기 어려움</t>
+          <t>미미한 효과 체감 — 맛과 복용 편의성은 좋으나 실제 몸이 나아지는 등의 뚜렷한 효과를 인지하기 어려움</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>다소 높은 가격대 — 제품의 가격대가 다소 비싸게 형성되어 있음</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>초반의 생소한 복용 방식 — 액상과 분말을 섞어 먹는 특이한 용기 방식이 처음에는 낯설 수 있음</t>
-        </is>
-      </c>
+          <t>높은 가격대 — 인기 있고 신뢰할 수 있는 제품이나 상시 복용하기에는 다소 비싼 편임</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>삼키기 부담스러운 알약 크기 — 기존 제품 대비 정제 크기가 커서 삼킬 때 다소 걸리는 느낌이 있음</t>
+          <t>부담스러운 알약 크기 — 기존 제품들에 비해 알약의 크기가 다소 커서 삼키기 어려울 수 있음</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4452,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -4512,7 +4509,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>아일로</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -4569,7 +4566,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
+          <t>'1입 증정' 아일로 타입1 콜라겐 비오틴 앰플 14일분 오간자 에디션 + 앰플 1입 추가 증정</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -4646,7 +4643,7 @@
         <v>1533</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>248</v>
+        <v>757</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>39</v>
@@ -4660,65 +4657,68 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>편안한 소화 및 배변 도움 — 식사 후 더부룩함을 줄여 소화를 돕고 배변 활동을 원활하게 만듦
-고소한 군고구마 맛 — 군고구마 맛이 나 거부감 없이 고소하고 맛있게 먹기 좋음</t>
+          <t>소화 및 배변 개선 — 식사 후 복용 시 소화가 편안하게 잘되고 배변 활동을 활발하게 해 줌
+고소하고 부담 없는 맛 — 군고구마 맛이 연상되는 고소한 맛으로 비리거나 부담스럽지 않게 섭취 가능함
+풍성한 사은품과 특가 — 할인 가격 혜택이 우수하며 사은품이나 한정 혜택 구성이 다채로움</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>말차와 딸기의 맛있는 조합 — 말차향과 딸기맛이 잘 어우러져 거부감 없이 맛있게 섭취 가능함
-아이돌 포토카드 혜택 — 콜라보 제품으로 포토카드와 엽서가 함께 제공되어 팬들의 만족도가 높음</t>
+          <t>훌륭한 맛의 조화 — 말차와 딸기의 맛이 적절하게 조합되어 특유의 텁텁함 없이 매우 맛있게 섭취 가능함
+알찬 콜라보 굿즈 제공 — 리센느 멤버의 포토카드와 엽서가 기본 포함되어 소장 욕구를 지닌 팬들에게 인기가 많음</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>정성스럽고 화려한 선물 포장 — 은은한 핑크 색상과 고급스러운 오간자 포장으로 선물 가치가 높음
-맑고 탱탱해지는 피부 체감 — 꾸준히 먹으면 피부가 탱탱해지고 맑아지는 느낌을 받음</t>
+          <t>매우 아름다운 선물 포장 — 은은한 핑크 오간자 리본 포장 등으로 정성과 고급스러움을 극대화하여 선물 가치를 높임
+피부 개선 및 편한 복용 — 액상 앰플 형태라 편하게 복용할 수 있으며 피부가 한결 맑아지고 탄력 있어지는 느낌을 줌</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>알찬 증정품과 가성비 — 저렴한 가격에 추가 증정 포와 과자까지 사은품으로 제공되어 혜택이 좋음
-맛있고 속 편한 소화 서포트 — 맛이 좋아 부담이 없으며 식사 후 소화에 도움을 줌</t>
+          <t>탁월한 소화 개선 효과 — 속이 더부룩하거나 소화가 잘 안 될 때 복용하면 뱃속이 한결 편안해짐
+가성비와 풍성한 증정 — 비교적 가격이 저렴하고 추가 증정 10포와 파로저당씬칩 과자 사은품까지 주어 만족스러움</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>골라 먹는 다양한 맛 구성 — 다양한 종류의 닭가슴살이 들어있어 질리지 않고 매일 골라 먹기 좋음
-실용적인 보냉백 증정 — 가격 대비 양이 푸짐하며 도시락용 보냉백까지 증정되어 활용도가 높음</t>
+          <t>질리지 않는 다양한 맛 — 종류가 다채롭게 구성되어 한 달간 지루하지 않게 골라 먹기 좋고 전반적으로 맛이 훌륭함
+실용적인 보냉백 증정 — 증정되는 보냉파우치의 크기가 넉넉하고 실용적이어서 평소 도시락을 싸 다닐 때 편리함
+합리적인 세트 가격 — 식단 관리를 위한 대용량 팩을 매우 경제적인 가격대에 풍성하게 구매할 수 있음</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>부드럽고 촉촉한 식감 — 닭가슴살 특유의 퍽퍽함이 전혀 없고 매우 부드러움
-가성비 좋은 패키지 구성 — 저렴한 가격대에 다양한 메뉴가 구성되어 다이어트 식단으로 적합함</t>
+          <t>부드럽고 훌륭한 식감 — 닭가슴살 특유의 뻑뻑함이 느껴지지 않을 정도로 부드러우며 자극적이지 않고 담백함
+가성비 넘치는 패키지 — 대량의 닭가슴살 팩을 3만 원 이하의 저렴하고 합리적인 비용에 구매할 수 있음
+간편하고 다양한 메뉴 — 메뉴가 획일적이지 않아 질리지 않고 물리지 않으며 전자레인지 간편 조리가 편리함</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>단백질 특유의 비린 맛 없음 — 텁텁함이나 비린 맛이 없고 일반 우유나 음료처럼 달콤하고 깔끔함
-속 편한 분리유청단백질 — 소화가 편한 성분으로 마신 후에도 속이 더부룩하지 않고 편안함
-휴대하기 편한 패키지 — 슬림한 용기로 가방에 넣고 다니며 운동 전후나 간식으로 마시기 용이함</t>
+          <t>깔끔하고 비리지 않은 맛 — 단백질 특유의 텁텁함과 비린 느낌이 없고 편의점 초코우유나 커피라떼처럼 맛있고 말끔함
+이상적인 영양 구성 — 단백질 20g을 포함한 풍부한 함량 대비 칼로리와 당이 낮아 부담 없이 다이어트에 활용함
+편안한 소화감 — 분리유청단백질이라서 마신 뒤에도 배앓이나 속 더부룩함이 유발되지 않고 속이 아주 편안함</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>신뢰할 수 있는 모델 추천 세트 — 김종국 추천 조합으로 아르기닌과 밀크씨슬을 함께 챙길 수 있어 알참
-확연한 피로 회복 및 활력 증진 — 아침에 일어날 때 몸이 가볍고 운동 시 지치지 않는 컨디션 유지에 도움 됨
-쇼핑백 증정으로 선물에 적합 — 고급스러운 쇼핑백이 함께 포함되어 지인이나 직장 동료 선물용으로 좋음</t>
+          <t>체감되는 피로 회복 — 아침에 일어날 때 몸이 가볍고 야근이나 운동 전후 활력과 지속력 보완에 효능이 뛰어남
+알차고 유용한 조합 — 피로 복구를 돕는 아르기닌 마카와 간 개선용 밀크씨슬을 합쳐 종합적 관리가 쉬움
+선물하기 좋은 고급 구성 — 쇼핑백이 기본 동봉되어 직장동료나 지인들의 축하 선물 및 건강 응원용으로 어울림</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>6200mg 초고함량 활력 충전 — 높은 아르기닌 함량으로 운동 퍼포먼스 향상과 피로 회복에 탁월함
-고급스러운 선물용 구성 — 패키지가 고급스럽고 추가 포와 전용 쇼핑백이 증정되어 선물용으로 뛰어남
-간편한 1포 섭취 및 휴대성 — 개별 포장되어 외출이나 운동 전 간편하게 1포씩 챙겨 먹기 좋음</t>
+          <t>상큼하고 비리지 않은 맛 — 가루형 특유의 냄새를 없애고 과일 맛의 상큼한 액상을 사용해 삼키기 좋고 비리지 않음
+공주풍의 예쁜 패키지 — 케이스와 병 외관 디자인이 무척 사랑스럽고 화려하여 시각적 만족감이 높음</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>상큼한 레몬 맛의 액상 제형 — 액상 스틱 형태로 물에 타서 부담 없이 맛있게 마실 수 있음
-운동 및 일상 활력 증진 — 복용 시 하루 시작이 가벼워지고 운동할 때 피로 회복과 기력 보충에 도움 됨</t>
+          <t>에너지 충전 및 활력 — 웨이트 트레이닝 전후 피로 개선과 활력 보완 및 근육 회복 보조에 도움을 줌
+편리한 액상과 좋은 맛 — 상큼한 레몬 맛의 액상 제형으로 물에 간편하게 희석해 먹기에 거부감이 없음
+뛰어난 휴대성 — 개별 슬림한 액상 스틱 형태로 제작되어 외출 시나 주머니에 간편히 챙기기 용이함</t>
         </is>
       </c>
     </row>
@@ -4730,35 +4730,39 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>구매 수량 제한의 불편함 — 선물용으로 대량 구매를 원해도 2개로 구매 수량이 제한되어 있음</t>
+          <t>제한적인 구매 수량 — 구매 가능한 수량 제한이 적용되어 여러 명에게 한 번에 대량으로 선물하기가 어려움</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>기존 효소 대비 적은 용량 — 기존에 판매하던 효소 제품에 비해 1포당 용량이 절반 정도로 적음</t>
+          <t>상대적으로 적은 용량 — 브랜드의 기존 다른 일반 카무트 효소 제품들과 비교 시 용량이 거의 반 정도에 그침</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>섭취 초반의 장 반응 — 복용 후 뱃속이 꾸르륵거리거나 방귀가 자주 나오는 현상이 있음
-최대 구매 수량 제한 — 1인당 최대 2개까지만 구매 가능하도록 수량이 제한되어 있음</t>
+          <t>구매 수량 제한의 불편 — 우수한 제품임에도 최대 2개 이상 구매하지 못하도록 수량이 한정되어 다량 구매가 불가능함
+초기 복부 팽만 및 가스 — 섭취 후 뱃속이 가스가 차서 꾸르륵거리거나 방귀가 자주 배출되는 반응이 일시적으로 나타남</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>배송 중 포장 터짐 현상 — 비닐 진공 포장이 헐렁하여 일부 제품이 터지고 소스가 새어 나오는 경우가 있음
-배송 시 제품 해동 — 배송 과정에서 제품이 많이 녹은 상태로 수령되는 사례가 있음</t>
+          <t>일부 팩의 포장 불량 — 진공포장이 불량하여 헐렁거리거나 배송 중에 터져 내용물 및 소스가 새어 나옴
+배송 중 해동 발생 — 냉동 상태로 신속히 도달하지 못해 수령 시점에 이미 해동이 꽤 진행되어 있음</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>배송 중 제품 해동 — 냉동 상태로 와야 할 제품이 배송 중 녹아서 도착하는 문제가 있음</t>
+          <t>배송 중 해동 현상 — 배송 도중 아이스팩 기능 저하 등의 문제로 수령 시 전제품이 해동되어 배송됨</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr"/>
       <c r="J21" s="3" t="inlineStr"/>
-      <c r="K21" s="3" t="inlineStr"/>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>다소 진한 액상 제형 — 액상이 고농축되어 맛이 다소 진하거나 강해 섭취 후 물을 한 잔 마셔야 할 수 있음</t>
+        </is>
+      </c>
       <c r="L21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
@@ -4809,7 +4813,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>43,900원</t>
+          <t>34,900원</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -5012,47 +5016,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
+          <t>종근당 데일리와이즈 혈당컷 다이어트 12정 12일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1,500원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253277&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306201&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260422/eIhoZ9JSC5jbp33vSbZX987253277_00_01eIhoZ9JSC5jbp33vSbZX.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260406/NBw0phjtTvR7tEfBicGr032306201_00_01NBw0phjtTvR7tEfBicGr.jpg</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J2" t="n">
-        <v>721</v>
+        <v>1209</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>타사 대비 압도적인 가성비 — 다른 브랜드 제품 대비 가격이 매우 저렴하고 함량이 뛰어남</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>물에 타 먹기 편한 맛 — 물에 타서 마시기 무난하고 맛있어 운동 전에 챙겨 먹기 좋음</t>
-        </is>
-      </c>
+          <t>가벼운 예방 관리 — 당 수치나 다이어트가 걱정될 때 사전에 편하게 복용하여 상태 예방하기에 무난함</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>불분명한 효능 체감 — 단기간 가볍게 예방 목적으로 먹다 보니 가시적인 호전이나 즉각적 체감이 더딤</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
@@ -5067,54 +5071,62 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>홀베리 유기농 레몬즙 10포</t>
+          <t>[산뜻한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 레몬＆민트 20캡슐 20일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>홀베리</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=965923434&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911102&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260305/6AQS4j3WbfucTbhmJ4ur965923434_00_006AQS4j3WbfucTbhmJ4ur.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260907/D3MtLfS4wvzyyoiG4ppT610911102_00_01D3MtLfS4wvzyyoiG4ppT.jpg</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="J3" t="n">
-        <v>1546</v>
+        <v>15</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>다양한 요리 및 음료 활용도 — 물에 타서 마시거나 잼, 각종 요리 부재료로 다양하게 쓰기 좋음</t>
+          <t>탁월한 가성비 — 올리브영 등 다른 매장에서 살 수 있는 시중가 대비 약 3분의 1 수준의 매우 저렴한 가격에 구매 가능함</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>위생적이고 편한 소포장 — 1회용 낱개 포장이라 휴대하기 쉽고 사용이 간편함</t>
+          <t>신속하고 강한 개운함 — 톡 씹는 즉시 상쾌한 레몬과 민트향이 터지며 입안을 시원하고 화하게 청결해지도록 도움</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>호불호 있는 맛과 크기 — 알갱이가 생각보다 큰 편이며 향이 다소 생소하거나 씹었을 때 맛에 대한 불호가 존재함</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>아쉬운 청량감 강도 — 기존에 나오던 다른 정통 민트볼들에 비하면 목이 뚫리는 듯한 강렬한 시원함은 조금 약함</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5122,12 +5134,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>홀베리 유기농 엑스트라버진 올리브유 10포</t>
+          <t>LG생활건강 이너뷰 콜라겐 더마스틱 7포</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>홀베리</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -5137,39 +5149,39 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032640075&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953528&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260312/0RECqyOK2V8qTztn2K7E032640075_00_000RECqyOK2V8qTztn2K7E.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250627/9Cz26kBHEVc4QcQuToeY994953528_00_009Cz26kBHEVc4QcQuToeY.jpg</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>4.7</v>
       </c>
       <c r="J4" t="n">
-        <v>1013</v>
+        <v>486</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>휴대하기 편한 파우치 형태 — 포 형태로 소분되어 있어 들고 다니며 음식에 뿌려 먹기 편함</t>
+          <t>간편한 한 포 복용 — 개별 포장된 액상형 스틱으로 한 포씩 손쉽게 복용할 수 있어 일상 소지가 유용함</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>부담 없이 체험 가능한 가격 — 대량 구매 전 소량으로 저렴하게 미리 먹어볼 수 있어 좋음</t>
+          <t>새콤한 맛과 가성비 — 새콤한 풍미를 선사하며 다이소 특성상 가성비 좋게 저분자 콜라겐을 챙길 수 있음</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>자극적이고 매운 맛 — 올리브유 특유의 매운맛이 강해 단독 섭취 시 풍미가 떨어지고 자극적임</t>
+          <t>원액의 아쉬운 맛 — 그냥 포장 자체로 원액만 짜 먹었을 때는 맛이 다소 진하고 아쉬워 물에 타서 복용해야 함</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>아쉬운 내용물 용량 — 포장에 비해 1포당 용량이 너무 적어 아쉬움이 남음</t>
+          <t>느린 효과 체감 — 일주일에서 이주일 가량의 짧은 복용 시 피부 탄력 개선 등 체감 효과가 눈에 띄게 나타나지 않음</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -5177,7 +5189,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -5185,12 +5197,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>닥터블릿 푸응 7 Days 슬립앤버닝 14정 7일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -5200,31 +5212,35 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306284&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260805/e483TrUWUwCko9CBv1Da032306284_00_00e483TrUWUwCko9CBv1Da.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>84</v>
+        <v>6428</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>수면 유도 및 체지방 감량 — 자기 전 복용 시 잠이 일찍 오게 도우며 급찐살을 빼는 데 효과적임</t>
+          <t>압도적인 가성비 — 비싼 가격에 형성되는 코엔자임 Q10을 아주 저렴한 금액대로 간편히 구매해 섭취가 가능함</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>부담 없는 저렴한 가격 — 다이소 특유의 저렴한 가격대로 단기 체중 관리에 가성비가 훌륭함</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>신뢰할 수 있는 성분 — 대웅제약 제조 상품이며 일반 유통 제품과 영양 구성에 차이가 없어 안심하고 복용함</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>일상의 피로감 감소 — 꾸준히 챙겨 먹다 보니 복용 전과 달리 매일 쌓이는 피로가 비교적 덜한 느낌을 얻음</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -5232,7 +5248,7 @@
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5240,12 +5256,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>락피도 티니핑 아르기닌스틱 12포 12일분</t>
+          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>락피도</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -5255,34 +5271,34 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=951817122&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000148&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260226/mCY81DaSP0EtG2BENK3D951817122_00_01mCY81DaSP0EtG2BENK3D.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/a7ohwSe3ShJimhwztOOK600000148_00_00a7ohwSe3ShJimhwztOOK.png</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>410</v>
+        <v>3360</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>아이들이 좋아하는 캐릭터 디자인 — 티니핑 캐릭터 패키지로 아이들의 선호도가 높아 즐겁게 섭취함</t>
+          <t>훌륭한 가격 대비 성능 — 부담 없는 저렴한 마트 가로 칼슘, 마그네슘, 비타민D 복합성분을 효율적으로 섭취 가능함</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>달콤한 자두 맛 간식 스틱 — 자두 맛이라 당 충전용 간식처럼 짜 먹거나 야근 시 물리기 좋음</t>
+          <t>부담 없는 알약 크기 — 정제의 알약 사이즈가 너무 거대하지 않아 목구멍으로 삼킬 때 거부감이 없음</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>아이 입맛에 따른 호불호 — 특유의 맛으로 인해 일부 아이들은 맛이 없다고 거부할 수 있음</t>
+          <t>효능 체감의 불확실성 — 일반 영양 보조제의 특성상 신체에 즉각적으로 드러나는 뚜렷한 건강 호전을 바로 알기는 힘듦</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
@@ -5291,7 +5307,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5299,7 +5315,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국 마이팝 발효효소＆매실</t>
+          <t>동국제약 혈당케어＆유산균 30캡슐</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -5309,39 +5325,39 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911031&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910678&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260623/AwS7hZ6EGxkGDWyKLCd8610911031_00_00AwS7hZ6EGxkGDWyKLCd8.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250829/y6DqUAmlgLsAXGUrvbmN610910678_00_00y6DqUAmlgLsAXGUrvbmN.png</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>155</v>
+        <v>1490</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>더부룩할 때 간편한 음용 — 휴대가 간편하여 속이 더부룩할 때 언제 어디서나 톡 따서 마시기 편함</t>
+          <t>매우 뛰어난 가성비 — 가격이 저렴하여 배송 기준 채우기 용이나 평소 데일리 가성비 유산균으로 부담 없이 구비함</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>저렴한 가격과 무난한 맛 — 매실 맛이라 맛이 우수하고 저렴하게 구매하여 챙겨 마시기 좋음</t>
+          <t>복합 기능에 대한 기대 — 식습관이 불규칙하여 우려되는 식후 혈당 스파이크 대처와 기본적인 장 건강 유산균을 함께 챙김</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>효능 체감의 불확실성 — 마시기에는 좋으나 뚜렷한 효능이나 변화는 느끼기 어려움</t>
+          <t>불분명한 혈당 조절 효과 — 단순 복용만으로는 실제 체내 혈당 관리에 얼마나 직접적이고 즉시적인 도움을 주는지 느끼기 힘듦</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
@@ -5385,31 +5401,23 @@
         <v>4.7</v>
       </c>
       <c r="J8" t="n">
-        <v>2643</v>
+        <v>2655</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1일 치 개별 포장의 편의성 — 하루 분량인 3캡슐씩 포장되어 있어 복용 여부를 쉽게 체크할 수 있음</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>체지방 감량 체감 효과 — 다이어트 효과가 뛰어나 주기적으로 재구매하여 먹기 좋음</t>
-        </is>
-      </c>
+          <t>다이어트 보조 효과 기대 — 유명 다이어트 브랜드 팻버닝 제품을 저렴하게 만나 체지방 감소에 도움을 줄 것이라 기대함</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>번거로운 일일 섭취 횟수 — 하루에 3번이나 나누어 챙겨 먹어야 하는 귀찮음이 있음</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5417,54 +5425,62 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>자연관 스파이크컷 바나바잎＆카테킨 4병</t>
+          <t>[옥수수수염＆호박] 동국제약 맛있는 센텔라 공주캔디 20정 20일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032627033&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911213&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260819/2NKz5YxykngJc58J5cja032627033_00_012NKz5YxykngJc58J5cja.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260907/E3CpURjLLswf9MgzRChF610911213_00_01E3CpURjLLswf9MgzRChF.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J9" t="n">
-        <v>337</v>
+        <v>21</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>바나바잎과 카테킨 복합 구성 — 혈당 관리 성분인 바나바잎과 녹차 카테킨이 함께 들어있어 유용함</t>
+          <t>다리 붓기 완화 효과 — 꾸준히 녹여 먹으면 아침이나 오후 다리에 쌓여있던 붓는 느낌이 비교적 가라앉음</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>부담 없는 가성비 — 가격이 저렴하여 건강 관리용으로 챙겨 먹기에 부담이 없음</t>
+          <t>귀여운 제품 컨셉 — 디자인 패키지가 아기자기하고 귀여운 스타일이며 공주캔디라는 이름이 흥미를 유발함</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>호불호 갈리는 맛 — 온전한 복숭아 맛보다는 인공적이거나 살짝 멀미약 같은 특이한 잔향이 느껴져 불호가 생길 수 있음</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>효과 없음의 개인차 — 사람의 체질이나 식습관 유무에 따라 붓기 개선 면에서 직접적 변화가 느껴지지 않을 수 있음</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr"/>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5472,49 +5488,53 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>자연관 정성담은 배도라지스틱 12포</t>
+          <t>대웅제약 비타민D 4000IU 30정 30일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=901762093&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000132&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260508/SdledEzpIdjdFFQW6W8g901762093_00_00SdledEzpIdjdFFQW6W8g.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/SvY5chCvz0QZIyP7AdTc600000132_00_00SvY5chCvz0QZIyP7AdTc.png</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>857</v>
+        <v>2895</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>기관지 진정 및 목 건강 도움 — 환절기나 겨울철 기침, 목통증이 있을 때 편하게 먹기 좋음</t>
+          <t>우수한 가격 경쟁력 — 고함량 비타민D3 단위를 시중 유통망 및 약국보다 훨씬 착한 마트 가격으로 구비함</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>편리한 휴대성과 착한 가격 — 스틱 형태로 휴대하기 쉽고 가격이 저렴하여 부담 없이 구매 가능함</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>높은 구매 접근성 — 약국에 직접 찾아갈 필요 없이 장을 보며 생활 매장에서 누구나 쉽고 신속하게 재구매함</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>믿을 수 있는 품질 — 약사 추천 영양제나 대중매체 동영상에서도 품질 우수성으로 검증받아 신뢰가 감</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>맛에 대한 호불호 존재 — 개인의 입맛에 따라 맛에 대한 선호도가 다소 갈릴 수 있음</t>
+          <t>다소 널널한 내부 포장 — 상대적으로 알약이 든 수량 대비 상자 내부의 여유 공간이 지나치게 커서 무의미해 보임</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -5523,7 +5543,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5531,12 +5551,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>대웅제약 비타민C 30정 30일분</t>
+          <t>오브맘 다이어트 홀릭 30포 15일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>오브맘</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -5546,34 +5566,30 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000127&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=913624075&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/V0qSVbLLgSaCWbYWEu73600000127_00_00V0qSVbLLgSaCWbYWEu73.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250519/2rLyPRrrXXN6XdvBMjj5913624075_00_002rLyPRrrXXN6XdvBMjj5.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J11" t="n">
-        <v>2630</v>
+        <v>995</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>영국산 원료의 극가성비 — 영국산 고함량 비타민C 1000mg을 5천원이라는 저렴한 가격에 구매 가능함</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>섭취가 편한 정제 형태 — 가루 제형에 비해 알약 형태라 매일 꾸준히 복용하기가 수월함</t>
-        </is>
-      </c>
+          <t>우수한 배변 촉진 효과 — 체중 감소를 목적으로 먹었으나 장을 자극해 변비 예방 및 부드러운 쾌변 활동에 만족감을 줌</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>체감 효과의 미비함 — 꾸준히 섭취해도 직접적인 효능은 즉각적으로 체감하기 어려움</t>
+          <t>미비한 체중 감량 효과 — 지방 연소나 몸무게가 실질적으로 감소하는 직접적 다이어트 작용의 체감은 불명확함</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -5700,42 +5716,42 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
+          <t>피부/미용</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>비타민D</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>비타민D</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
         </is>
       </c>
     </row>
@@ -5747,52 +5763,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>홀베리</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>홀베리</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>동국제약</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
           <t>닥터블릿</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>락피도</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>동국제약</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>닥터블릿</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>자연관</t>
-        </is>
-      </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>오브맘</t>
         </is>
       </c>
     </row>
@@ -5804,32 +5820,32 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
+          <t>종근당 데일리와이즈 혈당컷 다이어트 12정 12일분</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>홀베리 유기농 레몬즙 10포</t>
+          <t>[산뜻한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 레몬＆민트 20캡슐 20일분</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>홀베리 유기농 엑스트라버진 올리브유 10포</t>
+          <t>LG생활건강 이너뷰 콜라겐 더마스틱 7포</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>닥터블릿 푸응 7 Days 슬립앤버닝 14정 7일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>락피도 티니핑 아르기닌스틱 12포 12일분</t>
+          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국 마이팝 발효효소＆매실</t>
+          <t>동국제약 혈당케어＆유산균 30캡슐</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -5839,17 +5855,17 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>자연관 스파이크컷 바나바잎＆카테킨 4병</t>
+          <t>[옥수수수염＆호박] 동국제약 맛있는 센텔라 공주캔디 20정 20일분</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>자연관 정성담은 배도라지스틱 12포</t>
+          <t>대웅제약 비타민D 4000IU 30정 30일분</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 비타민C 30정 30일분</t>
+          <t>오브맘 다이어트 홀릭 30포 15일분</t>
         </is>
       </c>
     </row>
@@ -5860,10 +5876,10 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>4.7</v>
@@ -5872,22 +5888,22 @@
         <v>4.8</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>4.7</v>
       </c>
       <c r="J6" s="3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K6" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="L6" s="3" t="n">
         <v>4.7</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>4.8</v>
       </c>
     </row>
     <row r="7">
@@ -5897,37 +5913,37 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>721</v>
+        <v>1209</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1546</v>
+        <v>15</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1013</v>
+        <v>486</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>84</v>
+        <v>6428</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>410</v>
+        <v>3360</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>155</v>
+        <v>1490</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>2643</v>
+        <v>2655</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>337</v>
+        <v>21</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>857</v>
+        <v>2895</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>2630</v>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -5935,62 +5951,61 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>타사 대비 압도적인 가성비 — 다른 브랜드 제품 대비 가격이 매우 저렴하고 함량이 뛰어남
-물에 타 먹기 편한 맛 — 물에 타서 마시기 무난하고 맛있어 운동 전에 챙겨 먹기 좋음</t>
+          <t>가벼운 예방 관리 — 당 수치나 다이어트가 걱정될 때 사전에 편하게 복용하여 상태 예방하기에 무난함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>다양한 요리 및 음료 활용도 — 물에 타서 마시거나 잼, 각종 요리 부재료로 다양하게 쓰기 좋음
-위생적이고 편한 소포장 — 1회용 낱개 포장이라 휴대하기 쉽고 사용이 간편함</t>
+          <t>탁월한 가성비 — 올리브영 등 다른 매장에서 살 수 있는 시중가 대비 약 3분의 1 수준의 매우 저렴한 가격에 구매 가능함
+신속하고 강한 개운함 — 톡 씹는 즉시 상쾌한 레몬과 민트향이 터지며 입안을 시원하고 화하게 청결해지도록 도움</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>휴대하기 편한 파우치 형태 — 포 형태로 소분되어 있어 들고 다니며 음식에 뿌려 먹기 편함
-부담 없이 체험 가능한 가격 — 대량 구매 전 소량으로 저렴하게 미리 먹어볼 수 있어 좋음</t>
+          <t>간편한 한 포 복용 — 개별 포장된 액상형 스틱으로 한 포씩 손쉽게 복용할 수 있어 일상 소지가 유용함
+새콤한 맛과 가성비 — 새콤한 풍미를 선사하며 다이소 특성상 가성비 좋게 저분자 콜라겐을 챙길 수 있음</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>수면 유도 및 체지방 감량 — 자기 전 복용 시 잠이 일찍 오게 도우며 급찐살을 빼는 데 효과적임
-부담 없는 저렴한 가격 — 다이소 특유의 저렴한 가격대로 단기 체중 관리에 가성비가 훌륭함</t>
+          <t>압도적인 가성비 — 비싼 가격에 형성되는 코엔자임 Q10을 아주 저렴한 금액대로 간편히 구매해 섭취가 가능함
+신뢰할 수 있는 성분 — 대웅제약 제조 상품이며 일반 유통 제품과 영양 구성에 차이가 없어 안심하고 복용함
+일상의 피로감 감소 — 꾸준히 챙겨 먹다 보니 복용 전과 달리 매일 쌓이는 피로가 비교적 덜한 느낌을 얻음</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>아이들이 좋아하는 캐릭터 디자인 — 티니핑 캐릭터 패키지로 아이들의 선호도가 높아 즐겁게 섭취함
-달콤한 자두 맛 간식 스틱 — 자두 맛이라 당 충전용 간식처럼 짜 먹거나 야근 시 물리기 좋음</t>
+          <t>훌륭한 가격 대비 성능 — 부담 없는 저렴한 마트 가로 칼슘, 마그네슘, 비타민D 복합성분을 효율적으로 섭취 가능함
+부담 없는 알약 크기 — 정제의 알약 사이즈가 너무 거대하지 않아 목구멍으로 삼킬 때 거부감이 없음</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>더부룩할 때 간편한 음용 — 휴대가 간편하여 속이 더부룩할 때 언제 어디서나 톡 따서 마시기 편함
-저렴한 가격과 무난한 맛 — 매실 맛이라 맛이 우수하고 저렴하게 구매하여 챙겨 마시기 좋음</t>
+          <t>매우 뛰어난 가성비 — 가격이 저렴하여 배송 기준 채우기 용이나 평소 데일리 가성비 유산균으로 부담 없이 구비함
+복합 기능에 대한 기대 — 식습관이 불규칙하여 우려되는 식후 혈당 스파이크 대처와 기본적인 장 건강 유산균을 함께 챙김</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>1일 치 개별 포장의 편의성 — 하루 분량인 3캡슐씩 포장되어 있어 복용 여부를 쉽게 체크할 수 있음
-체지방 감량 체감 효과 — 다이어트 효과가 뛰어나 주기적으로 재구매하여 먹기 좋음</t>
+          <t>다이어트 보조 효과 기대 — 유명 다이어트 브랜드 팻버닝 제품을 저렴하게 만나 체지방 감소에 도움을 줄 것이라 기대함</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>바나바잎과 카테킨 복합 구성 — 혈당 관리 성분인 바나바잎과 녹차 카테킨이 함께 들어있어 유용함
-부담 없는 가성비 — 가격이 저렴하여 건강 관리용으로 챙겨 먹기에 부담이 없음</t>
+          <t>다리 붓기 완화 효과 — 꾸준히 녹여 먹으면 아침이나 오후 다리에 쌓여있던 붓는 느낌이 비교적 가라앉음
+귀여운 제품 컨셉 — 디자인 패키지가 아기자기하고 귀여운 스타일이며 공주캔디라는 이름이 흥미를 유발함</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>기관지 진정 및 목 건강 도움 — 환절기나 겨울철 기침, 목통증이 있을 때 편하게 먹기 좋음
-편리한 휴대성과 착한 가격 — 스틱 형태로 휴대하기 쉽고 가격이 저렴하여 부담 없이 구매 가능함</t>
+          <t>우수한 가격 경쟁력 — 고함량 비타민D3 단위를 시중 유통망 및 약국보다 훨씬 착한 마트 가격으로 구비함
+높은 구매 접근성 — 약국에 직접 찾아갈 필요 없이 장을 보며 생활 매장에서 누구나 쉽고 신속하게 재구매함
+믿을 수 있는 품질 — 약사 추천 영양제나 대중매체 동영상에서도 품질 우수성으로 검증받아 신뢰가 감</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>영국산 원료의 극가성비 — 영국산 고함량 비타민C 1000mg을 5천원이라는 저렴한 가격에 구매 가능함
-섭취가 편한 정제 형태 — 가루 제형에 비해 알약 형태라 매일 꾸준히 복용하기가 수월함</t>
+          <t>우수한 배변 촉진 효과 — 체중 감소를 목적으로 먹었으나 장을 자극해 변비 예방 및 부드러운 쾌변 활동에 만족감을 줌</t>
         </is>
       </c>
     </row>
@@ -6000,39 +6015,49 @@
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>불분명한 효능 체감 — 단기간 가볍게 예방 목적으로 먹다 보니 가시적인 호전이나 즉각적 체감이 더딤</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>호불호 있는 맛과 크기 — 알갱이가 생각보다 큰 편이며 향이 다소 생소하거나 씹었을 때 맛에 대한 불호가 존재함
+아쉬운 청량감 강도 — 기존에 나오던 다른 정통 민트볼들에 비하면 목이 뚫리는 듯한 강렬한 시원함은 조금 약함</t>
+        </is>
+      </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>자극적이고 매운 맛 — 올리브유 특유의 매운맛이 강해 단독 섭취 시 풍미가 떨어지고 자극적임
-아쉬운 내용물 용량 — 포장에 비해 1포당 용량이 너무 적어 아쉬움이 남음</t>
+          <t>원액의 아쉬운 맛 — 그냥 포장 자체로 원액만 짜 먹었을 때는 맛이 다소 진하고 아쉬워 물에 타서 복용해야 함
+느린 효과 체감 — 일주일에서 이주일 가량의 짧은 복용 시 피부 탄력 개선 등 체감 효과가 눈에 띄게 나타나지 않음</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>아이 입맛에 따른 호불호 — 특유의 맛으로 인해 일부 아이들은 맛이 없다고 거부할 수 있음</t>
+          <t>효능 체감의 불확실성 — 일반 영양 보조제의 특성상 신체에 즉각적으로 드러나는 뚜렷한 건강 호전을 바로 알기는 힘듦</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>효능 체감의 불확실성 — 마시기에는 좋으나 뚜렷한 효능이나 변화는 느끼기 어려움</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>번거로운 일일 섭취 횟수 — 하루에 3번이나 나누어 챙겨 먹어야 하는 귀찮음이 있음</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr"/>
+          <t>불분명한 혈당 조절 효과 — 단순 복용만으로는 실제 체내 혈당 관리에 얼마나 직접적이고 즉시적인 도움을 주는지 느끼기 힘듦</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>호불호 갈리는 맛 — 온전한 복숭아 맛보다는 인공적이거나 살짝 멀미약 같은 특이한 잔향이 느껴져 불호가 생길 수 있음
+효과 없음의 개인차 — 사람의 체질이나 식습관 유무에 따라 붓기 개선 면에서 직접적 변화가 느껴지지 않을 수 있음</t>
+        </is>
+      </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>맛에 대한 호불호 존재 — 개인의 입맛에 따라 맛에 대한 선호도가 다소 갈릴 수 있음</t>
+          <t>다소 널널한 내부 포장 — 상대적으로 알약이 든 수량 대비 상자 내부의 여유 공간이 지나치게 커서 무의미해 보임</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>체감 효과의 미비함 — 꾸준히 섭취해도 직접적인 효능은 즉각적으로 체감하기 어려움</t>
+          <t>미비한 체중 감량 효과 — 지방 연소나 몸무게가 실질적으로 감소하는 직접적 다이어트 작용의 체감은 불명확함</t>
         </is>
       </c>
     </row>
@@ -6044,34 +6069,34 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>1,500원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>2,000원</t>
-        </is>
-      </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
@@ -6079,12 +6104,12 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -6268,7 +6293,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -6276,42 +6301,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[딥트3일/남규리Pick]남규리의 바른 효소 리셋 8포</t>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>딥트3일</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>16,000원</t>
+          <t>30,400원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000211396&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021139617ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="J2" t="n">
-        <v>707</v>
+        <v>24376</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>탄수화물 커팅과 안색 개선 — 효소의 탄수화물 분해와 글루타치온의 간 건강 및 피부 안색 개선을 동시에 돕는 필수템임</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+          <t>뛰어난 장 건강 개선 — 공복 물 한 잔과 복용 시 유해균 감소 및 장 속 예민함을 정리하고 배변을 수월히 하도록 도움</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>간편한 알약 제형 — 이뮨 비타민 등 다른 기획 제품과 다르게 상부 알약 케이스가 없어 아주 간단히 캡슐만 목넘김함</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>알찬 사은품 및 기획 — 더블 기획으로 복용 분량이 알차며 한정 연예인 포토카드 및 추가 영양제 사은품이 우수함</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -6327,39 +6360,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[50억 보장] 그린몬스터 이너블라썸 질 유래 유산균 30캡슐 (1개월분)</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>그린몬스터</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>16,900원</t>
+          <t>31,400원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000172168&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017216854ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J3" t="n">
+        <v>8155</v>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>특허 코팅 기술의 유산균 — 듀라벡 코팅 기술을 적용하여 위산과 열에 약한 유산균을 장까지 안전하게 전달함</t>
+          <t>만족스러운 사은품 구성 — 카카오 단독 협업 인형 키링이나 유명 연예인 사진 카드 등 소장하기 좋은 부록을 함께 받음</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>합리적인 가격의 여성 유산균 — 고가 제품과 비교해도 차이가 없어 저렴한 가격에 정착하기 좋은 질유산균임</t>
+          <t>여성 맞춤형 이너케어 — 장 건강과 동시에 질 면역 유래 유산균을 보충하며 철분제 등 여성 전용 영양 공급이 용이함</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -6378,42 +6415,58 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비타바움 비타민B12 40000% 플러스 브이 컴플렉스 8 (30병입) (1개월분)</t>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>비타바움</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>95,000원</t>
+          <t>16,900원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000251282&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0025/A00000025128205ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J4" t="n">
+        <v>15080</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>강력한 수면 유도 효과 — 뒤척이거나 예민하여 불면이 찾아왔을 때 복용 후 깊은 수면 단계에 들어가도록 지원함</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>젤리 제형의 뛰어난 맛 — 맛없고 불편한 가루나 태블릿 형태가 아니며 간식처럼 달콤하게 씹어 넘길 수 있어 맛있음</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>양치 필요성의 번거로움 — 취침 직전 먹을 수 있는 젤리 형태이다 보니 섭취 후 반드시 양치질을 다시 해야 해 귀찮음</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -6421,46 +6474,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+          <t>올더베러 웰니스 구미 30일분 택1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>올더베러</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>31,400원</t>
+          <t>9,200원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245874&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024587418ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>8153</v>
+        <v>4796</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>풍성한 굿즈 및 사은품 구성 — 캐릭터 키링, 포토카드, 추가 영양제 등 알찬 증정 혜택을 제공함</t>
+          <t>맛있는 피로 회복 간식 — 레몬라임 등 달콤상콤한 구미 젤리 맛으로 업무 중간에 에너지와 콜라겐을 간편히 섭취함</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1일 1캡슐 간편한 케어 — 아침 공복에 하루 한 알 섭취하여 장과 질 건강을 동시에 케어하기 편함</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>물 없는 간편한 섭취 — 외출 시나 가방, 차량 안에서도 번거로움이나 식수 없이 간편하게 씹어서 흡수 가능함</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>합리적인 가격선 — 브랜드 유통가가 은근히 저렴하고 세일 및 할인 폭이 넓어 장바구니에 쟁이기 좋음</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -6468,7 +6525,7 @@
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -6476,37 +6533,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14입+1입 증정 기획 (2주분)</t>
+          <t>[50억 보장] 그린몬스터 이너블라썸 질 유래 유산균 30캡슐 (1개월분)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>그린몬스터</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>53,900원</t>
+          <t>16,900원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000171584&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000172168&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017158410ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017216854ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>4.9</v>
       </c>
       <c r="J6" t="n">
-        <v>6835</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+        <v>3174</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>뛰어난 가성비와 정착력 — 다른 비싼 고가 브랜드들과의 성능 차이가 느껴지지 않을 만큼 질 유산균 가성비 정착용으로 훌륭함</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>우수한 이너 케어 — 꽉 끼는 하의 착용 및 규칙적인 운동을 즐기는 여성이 섭취하면 확실히 신체 편안함이 달라짐</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -6515,7 +6580,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -6523,45 +6588,33 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[파격특가] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
+          <t>박카스O액 30ml 5개입(5일분)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>박카스</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>18,800원</t>
+          <t>11,200원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000183645&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000261747&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018364587ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J7" t="n">
-        <v>16998</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>확실한 배변 및 뱃살 감량 — 화장실을 잘 가도록 도우며 과식 후 붓기와 더부룩한 뱃살을 줄여줌</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>다양한 제형의 관리 라인업 — 젤리, 캡슐, 디톡스 클렌즈 주스 등 다양한 구성으로 상황별 관리가 가능함</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026174704ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -6570,7 +6623,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -6578,45 +6631,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[웰니스 루틴] 온리추얼 슬리밍컷 다이어트/리셋 브이라인/글로우업 콜라겐 7포(+1포)/14포 (8/14일분)</t>
+          <t>[1+1] 히말라야 숙취해소제 파티스마트 츄 [망고맛] 10P</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>온리추얼</t>
+          <t>히말라야</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>11,900원</t>
+          <t>13,900원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000236701&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000229743&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023670140ko.png?l=ko</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J8" t="n">
-        <v>18786</v>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022974325ko.png?l=ko</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>맛있는 간식 대체 젤리 — 새콤달콤하고 치아시드가 씹히는 탱글한 식감으로 간식 욕구를 대체해 줌</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>체지방 및 라인 관리 도움 — 가르시니아와 식이섬유 성분이 들어있어 체지방 감량 및 붓기 관리에 유용함</t>
-        </is>
-      </c>
+          <t>음주 생활 필수품 — 숙취가 잦은 30대 음주인들에게 대중적이고 확실한 주량 케어용 필수템으로 애용됨</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -6633,58 +6678,58 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>바이오코어유산균</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>13,950원</t>
+          <t>39,800원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000200143&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020014345ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J9" t="n">
-        <v>12531</v>
+        <v>494</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>속 편한 장 및 피부 면역 케어 — 복통이나 가스 차는 현상 없이 화장실을 잘 가고 피부 면역 증진에도 도움 됨</t>
+          <t>실용적인 이중 기능성 — 식약처 체지방 감소 인정을 받아 더부룩한 배를 장 건강 유산균과 함께 동시에 케어가 가능함</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>귀여운 캐릭터 콜라보 패키지 — 산리오 러기지택 증정 등 만족스러운 캐릭터 콜라보 구성을 제공함</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>다소 큰 알약 크기 — 기존 먹던 다른 유산균 제품들에 비해 알약 사이즈가 약간 크게 느껴짐</t>
-        </is>
-      </c>
+          <t>약사 배합의 높은 신뢰 — 국가대표 섭취 및 전문 약사 특허 배합 제품이라는 점에서 다이어트 관리 시 안도감을 줌</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>상큼한 요거트 맛 — 유산균 고유의 부드럽고 새콤한 요거트 가루 맛이라 물 없이 한 포씩 먹기 유용함</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -6692,49 +6737,53 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>올더베러 웰니스 구미 30일분 택1</t>
+          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>올더베러</t>
+          <t>바이오코어유산균</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>9,200원</t>
+          <t>13,950원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245874&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000200143&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024587418ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020014345ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>4793</v>
+        <v>12534</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>상큼하고 쫀득한 구미 제형 — 상큼한 맛과 쫀득한 식감으로 물 없이 간식처럼 간편하게 먹기 좋음</t>
+          <t>통증 없는 원활한 쾌변 — 100억 혹은 500억 보장 균수로 배가 기분 나쁘게 아프지 않으면서 편안하게 가스를 해소하고 화장실을 가게 함</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>합리적인 가격과 다양한 선택지 — 가격대가 합리적이며 구미, 오일, 에너지 샷 등 컨디션별 루틴 선택이 가능함</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>귀여운 산리오 콜라보 — 산리오 디자인과 협업하여 아기자기한 캐릭터 러기지택 등을 한정 제공해 구매 흥미를 줌</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>피부와 장의 종합 개선 — 꾸준한 섭취를 통해 피부 장벽 면역을 함께 건강하게 보강하여 이너뷰티 전반을 개선함</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>취침 전 섭취 시 양치 번거로움 — 젤리 제형 특성상 밤늦게 섭취할 경우 양치를 다시 해야 하는 불편함이 있음</t>
+          <t>다소 큰 알약 크기 — 기타 표준 유산균들과 대조 시 알약 캡슐의 물리적인 사이즈가 조금 더 큰 편에 속함</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -6751,36 +6800,40 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>솔티스눈 프로텍션 프로 S3 20캡슐 (20일분)</t>
+          <t>[딥트3일/남규리Pick]남규리의 바른 효소 리셋 8포</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>솔티스</t>
+          <t>딥트3일</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>12,900원</t>
+          <t>16,000원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000234147&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000211396&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023414702ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021139617ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J11" t="n">
-        <v>109</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
+        <v>707</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>탄수화물 컷팅 효과 — 빵이나 밥 등 면류 섭취 비중이 높을 때 식후 혈당 및 속의 더부룩함을 분해해 주는 용도로 유용함</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -6898,47 +6951,47 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -6955,52 +7008,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>멜라메이트</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>올더베러</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>그린몬스터</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>박카스</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>히말라야</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>프로뉴트리션</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>바이오코어유산균</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
           <t>딥트3일</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>그린몬스터</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>비타바움</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>덴프스</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>오쏘몰</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>푸드올로지</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>온리추얼</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>바이오코어유산균</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>올더베러</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>솔티스</t>
         </is>
       </c>
     </row>
@@ -7012,52 +7065,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>올더베러 웰니스 구미 30일분 택1</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>[50억 보장] 그린몬스터 이너블라썸 질 유래 유산균 30캡슐 (1개월분)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>박카스O액 30ml 5개입(5일분)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>[1+1] 히말라야 숙취해소제 파티스마트 츄 [망고맛] 10P</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
           <t>[딥트3일/남규리Pick]남규리의 바른 효소 리셋 8포</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>[50억 보장] 그린몬스터 이너블라썸 질 유래 유산균 30캡슐 (1개월분)</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>비타바움 비타민B12 40000% 플러스 브이 컴플렉스 8 (30병입) (1개월분)</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14입+1입 증정 기획 (2주분)</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>[파격특가] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>[웰니스 루틴] 온리추얼 슬리밍컷 다이어트/리셋 브이라인/글로우업 콜라겐 7포(+1포)/14포 (8/14일분)</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>올더베러 웰니스 구미 30일분 택1</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>솔티스눈 프로텍션 프로 S3 20캡슐 (20일분)</t>
         </is>
       </c>
     </row>
@@ -7068,30 +7121,30 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" s="3" t="inlineStr"/>
+        <v>4.9</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>4.8</v>
+      </c>
       <c r="F6" s="3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="H6" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>4.9</v>
-      </c>
+      <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="7">
@@ -7101,33 +7154,33 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
+        <v>24376</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>8155</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>15080</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>4796</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>3174</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="n">
+        <v>494</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>12534</v>
+      </c>
+      <c r="L7" s="3" t="n">
         <v>707</v>
       </c>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="n">
-        <v>8153</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>6835</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>16998</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>18786</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>12531</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>4793</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
+    </row>
+    <row r="8" ht="90" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -7135,48 +7188,61 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>탄수화물 커팅과 안색 개선 — 효소의 탄수화물 분해와 글루타치온의 간 건강 및 피부 안색 개선을 동시에 돕는 필수템임</t>
+          <t>뛰어난 장 건강 개선 — 공복 물 한 잔과 복용 시 유해균 감소 및 장 속 예민함을 정리하고 배변을 수월히 하도록 도움
+간편한 알약 제형 — 이뮨 비타민 등 다른 기획 제품과 다르게 상부 알약 케이스가 없어 아주 간단히 캡슐만 목넘김함
+알찬 사은품 및 기획 — 더블 기획으로 복용 분량이 알차며 한정 연예인 포토카드 및 추가 영양제 사은품이 우수함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>특허 코팅 기술의 유산균 — 듀라벡 코팅 기술을 적용하여 위산과 열에 약한 유산균을 장까지 안전하게 전달함
-합리적인 가격의 여성 유산균 — 고가 제품과 비교해도 차이가 없어 저렴한 가격에 정착하기 좋은 질유산균임</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr"/>
+          <t>만족스러운 사은품 구성 — 카카오 단독 협업 인형 키링이나 유명 연예인 사진 카드 등 소장하기 좋은 부록을 함께 받음
+여성 맞춤형 이너케어 — 장 건강과 동시에 질 면역 유래 유산균을 보충하며 철분제 등 여성 전용 영양 공급이 용이함</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>강력한 수면 유도 효과 — 뒤척이거나 예민하여 불면이 찾아왔을 때 복용 후 깊은 수면 단계에 들어가도록 지원함
+젤리 제형의 뛰어난 맛 — 맛없고 불편한 가루나 태블릿 형태가 아니며 간식처럼 달콤하게 씹어 넘길 수 있어 맛있음</t>
+        </is>
+      </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>풍성한 굿즈 및 사은품 구성 — 캐릭터 키링, 포토카드, 추가 영양제 등 알찬 증정 혜택을 제공함
-1일 1캡슐 간편한 케어 — 아침 공복에 하루 한 알 섭취하여 장과 질 건강을 동시에 케어하기 편함</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>확실한 배변 및 뱃살 감량 — 화장실을 잘 가도록 도우며 과식 후 붓기와 더부룩한 뱃살을 줄여줌
-다양한 제형의 관리 라인업 — 젤리, 캡슐, 디톡스 클렌즈 주스 등 다양한 구성으로 상황별 관리가 가능함</t>
-        </is>
-      </c>
+          <t>맛있는 피로 회복 간식 — 레몬라임 등 달콤상콤한 구미 젤리 맛으로 업무 중간에 에너지와 콜라겐을 간편히 섭취함
+물 없는 간편한 섭취 — 외출 시나 가방, 차량 안에서도 번거로움이나 식수 없이 간편하게 씹어서 흡수 가능함
+합리적인 가격선 — 브랜드 유통가가 은근히 저렴하고 세일 및 할인 폭이 넓어 장바구니에 쟁이기 좋음</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>뛰어난 가성비와 정착력 — 다른 비싼 고가 브랜드들과의 성능 차이가 느껴지지 않을 만큼 질 유산균 가성비 정착용으로 훌륭함
+우수한 이너 케어 — 꽉 끼는 하의 착용 및 규칙적인 운동을 즐기는 여성이 섭취하면 확실히 신체 편안함이 달라짐</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 간식 대체 젤리 — 새콤달콤하고 치아시드가 씹히는 탱글한 식감으로 간식 욕구를 대체해 줌
-체지방 및 라인 관리 도움 — 가르시니아와 식이섬유 성분이 들어있어 체지방 감량 및 붓기 관리에 유용함</t>
+          <t>음주 생활 필수품 — 숙취가 잦은 30대 음주인들에게 대중적이고 확실한 주량 케어용 필수템으로 애용됨</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>속 편한 장 및 피부 면역 케어 — 복통이나 가스 차는 현상 없이 화장실을 잘 가고 피부 면역 증진에도 도움 됨
-귀여운 캐릭터 콜라보 패키지 — 산리오 러기지택 증정 등 만족스러운 캐릭터 콜라보 구성을 제공함</t>
+          <t>실용적인 이중 기능성 — 식약처 체지방 감소 인정을 받아 더부룩한 배를 장 건강 유산균과 함께 동시에 케어가 가능함
+약사 배합의 높은 신뢰 — 국가대표 섭취 및 전문 약사 특허 배합 제품이라는 점에서 다이어트 관리 시 안도감을 줌
+상큼한 요거트 맛 — 유산균 고유의 부드럽고 새콤한 요거트 가루 맛이라 물 없이 한 포씩 먹기 유용함</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>상큼하고 쫀득한 구미 제형 — 상큼한 맛과 쫀득한 식감으로 물 없이 간식처럼 간편하게 먹기 좋음
-합리적인 가격과 다양한 선택지 — 가격대가 합리적이며 구미, 오일, 에너지 샷 등 컨디션별 루틴 선택이 가능함</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr"/>
+          <t>통증 없는 원활한 쾌변 — 100억 혹은 500억 보장 균수로 배가 기분 나쁘게 아프지 않으면서 편안하게 가스를 해소하고 화장실을 가게 함
+귀여운 산리오 콜라보 — 산리오 디자인과 협업하여 아기자기한 캐릭터 러기지택 등을 한정 제공해 구매 흥미를 줌
+피부와 장의 종합 개선 — 꾸준한 섭취를 통해 피부 장벽 면역을 함께 건강하게 보강하여 이너뷰티 전반을 개선함</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>탄수화물 컷팅 효과 — 빵이나 밥 등 면류 섭취 비중이 높을 때 식후 혈당 및 속의 더부룩함을 분해해 주는 용도로 유용함</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="1" t="inlineStr">
@@ -7186,19 +7252,19 @@
       </c>
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>양치 필요성의 번거로움 — 취침 직전 먹을 수 있는 젤리 형태이다 보니 섭취 후 반드시 양치질을 다시 해야 해 귀찮음</t>
+        </is>
+      </c>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>다소 큰 알약 크기 — 기존 먹던 다른 유산균 제품들에 비해 알약 사이즈가 약간 크게 느껴짐</t>
-        </is>
-      </c>
+      <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>취침 전 섭취 시 양치 번거로움 — 젤리 제형 특성상 밤늦게 섭취할 경우 양치를 다시 해야 하는 불편함이 있음</t>
+          <t>다소 큰 알약 크기 — 기타 표준 유산균들과 대조 시 알약 캡슐의 물리적인 사이즈가 조금 더 큰 편에 속함</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr"/>
@@ -7211,52 +7277,52 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>30,400원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>31,400원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>16,900원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>9,200원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>16,900원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>11,200원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>13,900원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>39,800원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>13,950원</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
           <t>16,000원</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>16,900원</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>95,000원</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>31,400원</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>53,900원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>18,800원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>11,900원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>13,950원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>9,200원</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>12,900원</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7386,19 +7452,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D2" t="n">
         <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -7408,19 +7474,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
         <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -7430,10 +7496,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>22.5</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
         <v>8</v>
@@ -7442,7 +7508,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -7452,10 +7518,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -7464,26 +7530,26 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
         <v>1</v>
-      </c>
-      <c r="C6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -7492,20 +7558,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -7514,7 +7580,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -7524,12 +7590,34 @@
         <v>2.5</v>
       </c>
       <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
         <v>1</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>0</v>
       </c>
-      <c r="F8" t="n">
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>홍삼/인삼</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
         <v>0</v>
       </c>
     </row>
